--- a/docs/demo-materials/contract-sample-tests/合同样例-测试导入样本-正常-920行.xlsx
+++ b/docs/demo-materials/contract-sample-tests/合同样例-测试导入样本-正常-920行.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入样本" sheetId="1" r:id="Rb78018d0ead8432e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" r:id="R4dc99c0568d14535"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="导入样本" sheetId="1" r:id="R06f30353f0e3471e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="2" r:id="R66062556d2334e94"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -87,7 +87,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NormalImportSamples" displayName="NormalImportSamples" ref="A1:B921" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="NormalImportSamples920" displayName="NormalImportSamples920" ref="A1:B921" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:B921"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="合同段落"/>
@@ -98,7 +98,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="NormalImportNotes" displayName="NormalImportNotes" ref="A1:B4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="NormalImportNotes920" displayName="NormalImportNotes920" ref="A1:B4" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
   <x:autoFilter ref="A1:B4"/>
   <x:tableColumns count="2">
     <x:tableColumn id="1" name="项目"/>
@@ -7678,7 +7678,7 @@
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra1ad39b2403a4be4"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R40e6539238d94bfc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -7704,29 +7704,29 @@
         <x:v>用途</x:v>
       </x:c>
       <x:c r="B2" s="7" t="str">
-        <x:v>用于正常导入演示，覆盖单标签、多标签、合同原文段落和轻微改写段落。</x:v>
+        <x:v>用于中等批量导入、同步Embedding、Oracle落库和索引刷新验证。</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
       <x:c r="A3" s="8" t="str">
-        <x:v>数据来源</x:v>
+        <x:v>结构检查</x:v>
       </x:c>
       <x:c r="B3" s="8" t="str">
-        <x:v>从样例合同抽取 958 条可用段落，并生成同主题改写样本。</x:v>
+        <x:v>920条段落文本唯一，不包含同段落不同编码冲突。</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
       <x:c r="A4" s="8" t="str">
-        <x:v>注意</x:v>
+        <x:v>重要限制</x:v>
       </x:c>
       <x:c r="B4" s="8" t="str">
-        <x:v>编码为演示标签，不代表真实业务人工标注结果。</x:v>
+        <x:v>变更类型编码为规则验证标签，不是人工业务标注，不用于判断预测准确率。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R8ee99a3a6e7c4770"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R043c475b7d3e4e1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>